--- a/data/trans_orig/AIRE_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Estudios-trans_orig.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>453</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19414</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26533</t>
+          <t>26653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31080</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45481</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56165</t>
+          <t>56317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>501</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>534</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>13251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27413</t>
+          <t>26837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23295</t>
+          <t>22954</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33773</t>
+          <t>35057</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45448</t>
+          <t>47000</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35255</t>
+          <t>35580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66441</t>
+          <t>64811</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>163067</t>
+          <t>163444</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>190338</t>
+          <t>188495</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>172257</t>
+          <t>173960</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>202586</t>
+          <t>203403</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>345744</t>
+          <t>343213</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>388927</t>
+          <t>387791</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>462</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>483</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>11160</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>14535</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>24061</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>23523</t>
+          <t>24170</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>40234</t>
+          <t>39870</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>46424</t>
+          <t>45453</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>60129</t>
+          <t>59901</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>55239</t>
+          <t>55911</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>71844</t>
+          <t>72022</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>106468</t>
+          <t>106098</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>128590</t>
+          <t>128132</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>15388</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>406</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>392</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>793</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>7123</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5390,82 +5390,82 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>6847</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>6565</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2233</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>11396</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>33432</t>
+          <t>34821</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>21289</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>30583</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>46832</t>
+          <t>46369</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>28112</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>49618</t>
+          <t>48235</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>33649</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>63238</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>67875</t>
+          <t>67027</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>102525</t>
+          <t>101617</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>236495</t>
+          <t>238447</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>272515</t>
+          <t>271852</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>261692</t>
+          <t>262850</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>296993</t>
+          <t>297538</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>510978</t>
+          <t>509862</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>561306</t>
+          <t>560684</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4568</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5135</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4965</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5317</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4825</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4752</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5019</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>14,38%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4170</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -1398,107 +1398,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3494</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4196</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>17,81%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4387</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4282</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -1511,107 +1511,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3292</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>3828</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>3236</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1624,72 +1624,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26,46%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2338</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8439</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>406</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -1737,72 +1737,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4245</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2498</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5910</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -1850,72 +1850,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25311</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19218</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28335</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,53%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>23958</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19505</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26653</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,38%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>21823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51872</t>
+          <t>44495</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45420</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56317</t>
+          <t>48905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -1963,74 +1963,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>23554</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>23554</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>23554</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>33052</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>33052</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>33052</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>78</t>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2193,72 +2193,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3266</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8823</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1238</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4849</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4819</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3344</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>8401</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -2306,107 +2306,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>945</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4818</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>4170</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>4647</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>4474</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2419,107 +2419,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2218</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1638</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2202</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -2532,107 +2532,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10525</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3611</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>10517</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2645,72 +2645,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>6021</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>383</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,22 +2720,22 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>489</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -2758,72 +2758,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8277</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4026</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14174</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>6849</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2550</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>13251</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26837</t>
+          <t>23935</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2984,72 +2984,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>14147</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8591</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>22709</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>9207</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>4541</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>15694</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22954</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>24315</t>
+          <t>23192</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35057</t>
+          <t>33058</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -3097,72 +3097,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>27970</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>20179</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>42093</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>18004</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>11065</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>26105</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>29497</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>26840</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>47501</t>
+          <t>46748</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35580</t>
+          <t>36571</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64811</t>
+          <t>62822</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -3210,72 +3210,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>175883</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>161565</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>188181</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>67,54%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>78,67%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>175045</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>163444</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>188495</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>80,78%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>75,43%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>86,99%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>189772</t>
+          <t>149014</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>173960</t>
+          <t>139057</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203403</t>
+          <t>158557</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>364817</t>
+          <t>324897</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>343213</t>
+          <t>307430</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>387791</t>
+          <t>339203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -3323,74 +3323,74 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>191243</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>191243</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>191243</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>258230</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>258230</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>258230</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>643</t>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3440,72 +3440,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2242</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6155</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2361</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2463</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8194</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -3553,72 +3553,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4141</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1538</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>8357</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3880</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3092</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>4713</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>9473</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -3666,107 +3666,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>4149</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>5111</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>4933</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -3779,107 +3779,107 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>4671</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>4295</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>4755</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>4537</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3892,107 +3892,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>2358</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>1682</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -4005,72 +4005,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>6037</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>4007</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>4489</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>6329</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>869</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -4118,72 +4118,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>3867</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>1450</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>8634</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -4231,72 +4231,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>5750</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2287</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>5458</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,22 +4306,22 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4344,72 +4344,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>6789</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>4253</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1550</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>8487</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -4457,72 +4457,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>13759</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>8800</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>20132</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>15,55%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>9,95%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>22,76%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>17752</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>12206</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>24454</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>14,35%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>31464</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24170</t>
+          <t>24979</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>39870</t>
+          <t>41283</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -4570,107 +4570,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>59544</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>52084</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>66995</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>67,31%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>58,88%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>53255</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>45453</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>59901</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>62,62%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>53,45%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>53003</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>45656</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>60535</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>62,01%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>53,41%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>70,82%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>112546</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>102136</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>122513</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>64,71%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>58,72%</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>70,44%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>64003</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>55911</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>72022</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>67,47%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>58,94%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>75,92%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>117258</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>106098</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>128132</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>65,18%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>58,97%</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -4683,74 +4683,74 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>85475</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>85475</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>85475</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>94867</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>94867</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>94867</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>257</t>
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,72 +4800,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>5178</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>10988</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>5533</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>363</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -4913,72 +4913,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>3802</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>14168</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>6159</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5731</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>8058</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>3974</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>13975</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5026,107 +5026,107 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>1915</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>6715</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>1915</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>6827</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -5139,72 +5139,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>5415</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>4502</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>324</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -5252,72 +5252,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>4483</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>12222</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2174</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>4548</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>11398</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>11836</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -5365,72 +5365,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>6644</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2951</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>6921</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>872</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,32 +5440,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>16953</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>15256</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>34821</t>
+          <t>31344</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -5591,72 +5591,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>4046</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>9413</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>6060</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>3015</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>11883</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>5849</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>10462</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>4487</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>10128</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,22 +5666,22 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>17364</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -5704,72 +5704,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>19070</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>12017</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>26732</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>13890</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>8248</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>21391</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>24086</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>46369</t>
+          <t>43712</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>42688</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>26913</t>
+          <t>32877</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>48235</t>
+          <t>58895</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5857,32 +5857,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>44135</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>61424</t>
+          <t>49262</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>82389</t>
+          <t>82392</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>67027</t>
+          <t>68401</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>101617</t>
+          <t>101521</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -5930,72 +5930,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>260739</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>244156</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>275967</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>72,84%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>68,21%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>345</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>252258</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>238447</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>271852</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>76,41%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>72,23%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>82,35%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221199</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>262850</t>
+          <t>208351</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>297538</t>
+          <t>233665</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>533947</t>
+          <t>481939</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>509862</t>
+          <t>460074</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>560684</t>
+          <t>501237</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -6043,74 +6043,74 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>467</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>300272</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>300272</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>300272</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>978</t>
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
